--- a/output/2026-10-02_09_Malesia_Melaka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-02_09_Malesia_Melaka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore MRO/utensili industriali con sede a Melaka (Taman Puncak Bertam); copertura nazionale Malesia. Esistenza e sede confermate via sito ufficiale e directory (NewPages).</t>
+          <t>Distributore MRO/utensili industriali con sede a Melaka (Taman Puncak Bertam); copertura nazionale Malesia. Esistenza e sede confermate via sito ufficiale e directory (NewPages). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore hardware industriale (utensili, macchine, valvole, pneumatica, saldatura), sede Taman Malim Jaya, Melaka. Confermato via sito ufficiale e directory.</t>
+          <t>Distributore hardware industriale (utensili, macchine, valvole, pneumatica, saldatura), sede Taman Malim Jaya, Melaka. Confermato via sito ufficiale e directory. [DUPLICATO — vedi anche: 2026-10-02_01_Malesia_Melaka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rivenditore hardware/utensili/PPE, sede Kuala Sungai Baru, Melaka. Confermato via sito ufficiale (Black Hardware, brand e-commerce di Nam Foh Hardware).</t>
+          <t>Rivenditore hardware/utensili/PPE, sede Kuala Sungai Baru, Melaka. Confermato via sito ufficiale (Black Hardware, brand e-commerce di Nam Foh Hardware). [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -684,7 +684,6 @@
           <t>Multitech Industry Supplies</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Melaka</t>
@@ -700,10 +699,9 @@
           <t>06-335 6992</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fornitore strumenti di misura/precisione (hardness tester, micrometri, CMM), sede Taman Industri Malim Jaya, Melaka dal 2004. Esistenza confermata via MachineTools.com e MelakaPages; sito web proprio non raggiungibile/non confermato, email non reperita: campi lasciati vuoti.</t>
+          <t>Fornitore strumenti di misura/precisione (hardness tester, micrometri, CMM), sede Taman Industri Malim Jaya, Melaka dal 2004. Esistenza confermata via MachineTools.com e MelakaPages; sito web proprio non raggiungibile/non confermato, email non reperita: campi lasciati vuoti. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -738,10 +736,9 @@
           <t>+606-336 3634</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Distributore utensili pneumatici, macchine utensili, raccordi rapidi, utensili a mano industriali dal 1979; filiale Batu Berendam, Melaka confermata via sito ufficiale. Email specifica della filiale non confermata: campo lasciato vuoto.</t>
+          <t>Distributore utensili pneumatici, macchine utensili, raccordi rapidi, utensili a mano industriali dal 1979; filiale Batu Berendam, Melaka confermata via sito ufficiale. Email specifica della filiale non confermata: campo lasciato vuoto. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -783,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Distributore accessori macchine CNC, rettifica, fresatura, utensili da taglio e abrasivi dal 1993; filiale Taman Malim Jaya, Melaka confermata via sito ufficiale e directory aziendali.</t>
+          <t>Distributore accessori macchine CNC, rettifica, fresatura, utensili da taglio e abrasivi dal 1993; filiale Taman Malim Jaya, Melaka confermata via sito ufficiale e directory aziendali. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -825,7 +822,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Distributore cuscinetti, automazione, viti a ricircolo di sfere; filiale Taman Malim Jaya, Melaka confermata via sito ufficiale e NewPages.</t>
+          <t>Distributore cuscinetti, automazione, viti a ricircolo di sfere; filiale Taman Malim Jaya, Melaka confermata via sito ufficiale e NewPages. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -867,7 +864,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dealer autorizzato Husqvarna, DongCheng, GL Bosun; macchinari agricoli, power tools, macchinari industriali. Sede Taman Malim Jaya, Melaka confermata via sito ufficiale, Husqvarna dealer locator e GL Bosun dealer list.</t>
+          <t>Dealer autorizzato Husqvarna, DongCheng, GL Bosun; macchinari agricoli, power tools, macchinari industriali. Sede Taman Malim Jaya, Melaka confermata via sito ufficiale, Husqvarna dealer locator e GL Bosun dealer list. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
